--- a/artfynd/A 48970-2025 artfynd.xlsx
+++ b/artfynd/A 48970-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79879769</v>
+        <v>79879783</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385945.2308793077</v>
+        <v>385927</v>
       </c>
       <c r="R2" t="n">
-        <v>6661663.142659851</v>
+        <v>6661623</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3-4 pyttesmå bålar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79879764</v>
+        <v>79879768</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385893.9453789074</v>
+        <v>385801</v>
       </c>
       <c r="R3" t="n">
-        <v>6661719.16695152</v>
+        <v>6661648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +840,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79879785</v>
+        <v>79879764</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386180.0444290017</v>
+        <v>385894</v>
       </c>
       <c r="R4" t="n">
-        <v>6661896.064562984</v>
+        <v>6661719</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +937,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,6 +963,399 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>79879767</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röllöberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>385801</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6661648</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>79879785</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Röllöberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>386180</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6661896</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>79879824</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röllöberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>386194</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6661860</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>79879769</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röllöberg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>385945</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6661663</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3-4 pyttesmå bålar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48970-2025 artfynd.xlsx
+++ b/artfynd/A 48970-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79879783</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79879768</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79879764</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79879767</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79879785</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79879824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,8 +1391,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79879769</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>